--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.3160,0.1245,0.0861,0.5717</t>
-  </si>
-  <si>
-    <t>0.0518,0.0052,0.0058,0.9770</t>
-  </si>
-  <si>
-    <t>0.6606,0.0384,0.0090,0.2973</t>
-  </si>
-  <si>
-    <t>0.2842,0.0195,0.0418,0.7702</t>
-  </si>
-  <si>
-    <t>0.9928,0.0038,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9913,0.0026,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.9937,0.0029,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9964,0.0024,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9913,0.0051,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9936,0.0008,0.0000,0.0016</t>
-  </si>
-  <si>
-    <t>0.9955,0.0005,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9968,0.0011,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.7573,0.0504,0.1340,0.0589</t>
-  </si>
-  <si>
-    <t>0.1494,0.0792,0.7879,0.0720</t>
-  </si>
-  <si>
-    <t>0.1133,0.0443,0.8767,0.0046</t>
-  </si>
-  <si>
-    <t>0.1857,0.0364,0.8430,0.0153</t>
-  </si>
-  <si>
-    <t>0.8694,0.0226,0.1150,0.0094</t>
-  </si>
-  <si>
-    <t>0.0385,0.9549,0.0079,0.0007</t>
-  </si>
-  <si>
-    <t>0.1390,0.9007,0.0052,0.0002</t>
-  </si>
-  <si>
-    <t>0.4132,0.7307,0.0053,0.0007</t>
-  </si>
-  <si>
-    <t>0.0906,0.9219,0.0051,0.0005</t>
-  </si>
-  <si>
-    <t>0.0930,0.9328,0.0026,0.0004</t>
-  </si>
-  <si>
-    <t>0.3365,0.0212,0.7377,0.0118</t>
-  </si>
-  <si>
-    <t>0.3111,0.0564,0.6611,0.0088</t>
-  </si>
-  <si>
-    <t>0.0420,0.0129,0.9479,0.0034</t>
-  </si>
-  <si>
-    <t>0.5721,0.0097,0.6133,0.0047</t>
-  </si>
-  <si>
-    <t>0.0372,0.0023,0.9676,0.0079</t>
-  </si>
-  <si>
-    <t>0.1119,0.0045,0.9172,0.0165</t>
-  </si>
-  <si>
-    <t>0.0010,0.0022,0.9940,0.0027</t>
-  </si>
-  <si>
-    <t>0.6979,0.3225,0.0454,0.0097</t>
-  </si>
-  <si>
-    <t>0.5145,0.2244,0.3570,0.0084</t>
-  </si>
-  <si>
-    <t>0.0013,0.0094,0.9902,0.0033</t>
-  </si>
-  <si>
-    <t>0.0159,0.9385,0.1476,0.0018</t>
-  </si>
-  <si>
-    <t>0.8312,0.1025,0.0554,0.0232</t>
-  </si>
-  <si>
-    <t>0.8323,0.1674,0.0343,0.0047</t>
-  </si>
-  <si>
-    <t>0.8717,0.2094,0.0039,0.0007</t>
-  </si>
-  <si>
-    <t>0.0775,0.8138,0.4012,0.0082</t>
-  </si>
-  <si>
-    <t>0.1455,0.3363,0.1304,0.1034</t>
-  </si>
-  <si>
-    <t>0.0032,0.0016,0.9500,0.1391</t>
-  </si>
-  <si>
-    <t>0.0277,0.4320,0.8183,0.0078</t>
-  </si>
-  <si>
-    <t>0.0055,0.0065,0.9815,0.0104</t>
-  </si>
-  <si>
-    <t>0.0035,0.0832,0.9809,0.0007</t>
-  </si>
-  <si>
-    <t>0.0024,0.9818,0.0297,0.0003</t>
-  </si>
-  <si>
-    <t>0.0132,0.3865,0.8779,0.0049</t>
-  </si>
-  <si>
-    <t>0.4811,0.1856,0.0255,0.3496</t>
-  </si>
-  <si>
-    <t>0.0190,0.9560,0.0124,0.0134</t>
-  </si>
-  <si>
-    <t>0.0061,0.9296,0.1598,0.0079</t>
-  </si>
-  <si>
-    <t>0.0100,0.9617,0.0347,0.0158</t>
-  </si>
-  <si>
-    <t>0.0079,0.0370,0.9804,0.0019</t>
-  </si>
-  <si>
-    <t>0.0036,0.2449,0.9669,0.0006</t>
-  </si>
-  <si>
-    <t>0.1939,0.0177,0.8213,0.0342</t>
-  </si>
-  <si>
-    <t>0.0807,0.0136,0.9228,0.0058</t>
-  </si>
-  <si>
-    <t>0.0053,0.0161,0.9892,0.0010</t>
-  </si>
-  <si>
-    <t>0.0016,0.0217,0.9898,0.0005</t>
-  </si>
-  <si>
-    <t>0.9767,0.0292,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.9760,0.0030,0.0009,0.0090</t>
-  </si>
-  <si>
-    <t>0.9426,0.0295,0.0161,0.0081</t>
-  </si>
-  <si>
-    <t>0.0062,0.0498,0.9841,0.0032</t>
-  </si>
-  <si>
-    <t>0.9909,0.0009,0.0002,0.0036</t>
-  </si>
-  <si>
-    <t>0.9936,0.0012,0.0003,0.0015</t>
-  </si>
-  <si>
-    <t>0.9581,0.0530,0.0029,0.0013</t>
-  </si>
-  <si>
-    <t>0.0021,0.6720,0.9482,0.0005</t>
-  </si>
-  <si>
-    <t>0.0169,0.1891,0.9586,0.0018</t>
-  </si>
-  <si>
-    <t>0.0031,0.7574,0.8666,0.0051</t>
-  </si>
-  <si>
-    <t>0.0003,0.9268,0.9471,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0063,0.9943,0.0017</t>
-  </si>
-  <si>
-    <t>0.0605,0.8877,0.0859,0.0079</t>
-  </si>
-  <si>
-    <t>0.0372,0.9548,0.0044,0.0015</t>
-  </si>
-  <si>
-    <t>0.3502,0.0418,0.7396,0.0033</t>
-  </si>
-  <si>
-    <t>0.7236,0.2718,0.0275,0.0113</t>
-  </si>
-  <si>
-    <t>0.0026,0.0873,0.9844,0.0006</t>
-  </si>
-  <si>
-    <t>0.0051,0.8841,0.6611,0.0007</t>
-  </si>
-  <si>
-    <t>0.0030,0.8796,0.7780,0.0005</t>
-  </si>
-  <si>
-    <t>0.0011,0.9399,0.8211,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.7791,0.8985,0.0014</t>
-  </si>
-  <si>
-    <t>0.3334,0.0010,0.0438,0.6288</t>
-  </si>
-  <si>
-    <t>0.0131,0.0014,0.0014,0.9941</t>
-  </si>
-  <si>
-    <t>0.0068,0.0018,0.0009,0.9963</t>
-  </si>
-  <si>
-    <t>0.0159,0.0019,0.0022,0.9916</t>
-  </si>
-  <si>
-    <t>0.0516,0.0034,0.0270,0.9533</t>
-  </si>
-  <si>
-    <t>0.0222,0.0043,0.0017,0.9902</t>
-  </si>
-  <si>
-    <t>0.0007,0.9126,0.9448,0.0003</t>
-  </si>
-  <si>
-    <t>0.0016,0.7015,0.9319,0.0001</t>
-  </si>
-  <si>
-    <t>0.0115,0.2668,0.8842,0.0018</t>
-  </si>
-  <si>
-    <t>0.0215,0.0811,0.9445,0.0012</t>
-  </si>
-  <si>
-    <t>0.0007,0.8613,0.9244,0.0001</t>
-  </si>
-  <si>
-    <t>0.0026,0.6993,0.8376,0.0003</t>
-  </si>
-  <si>
-    <t>0.9944,0.0032,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.9807,0.0132,0.0040,0.0012</t>
-  </si>
-  <si>
-    <t>0.9939,0.0060,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9941,0.0018,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9923,0.0073,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9978,0.0005,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9840,0.0058,0.0009,0.0019</t>
-  </si>
-  <si>
-    <t>0.9841,0.0069,0.0018,0.0021</t>
-  </si>
-  <si>
-    <t>0.9978,0.0002,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0003,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9899,0.0055,0.0009,0.0008</t>
-  </si>
-  <si>
-    <t>0.9981,0.0011,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9948,0.0007,0.0002,0.0016</t>
-  </si>
-  <si>
-    <t>0.9982,0.0002,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0043,0.0020,0.9901,0.0057</t>
-  </si>
-  <si>
-    <t>0.0301,0.0084,0.9626,0.0051</t>
-  </si>
-  <si>
-    <t>0.8806,0.0070,0.1157,0.0122</t>
-  </si>
-  <si>
-    <t>0.0201,0.0304,0.9489,0.0089</t>
-  </si>
-  <si>
-    <t>0.0519,0.9502,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.0340,0.9692,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.1623,0.8543,0.0016,0.0039</t>
-  </si>
-  <si>
-    <t>0.3209,0.7884,0.0044,0.0021</t>
-  </si>
-  <si>
-    <t>0.0533,0.9409,0.0046,0.0020</t>
-  </si>
-  <si>
-    <t>0.0941,0.9182,0.0124,0.0005</t>
-  </si>
-  <si>
-    <t>0.6474,0.4779,0.0079,0.0040</t>
-  </si>
-  <si>
-    <t>0.1807,0.7485,0.1650,0.0247</t>
-  </si>
-  <si>
-    <t>0.2325,0.0350,0.7846,0.0082</t>
-  </si>
-  <si>
-    <t>0.5478,0.2835,0.1694,0.0173</t>
-  </si>
-  <si>
-    <t>0.4999,0.0763,0.5060,0.0124</t>
-  </si>
-  <si>
-    <t>0.3873,0.2688,0.2417,0.3728</t>
-  </si>
-  <si>
-    <t>0.0134,0.9541,0.1150,0.0124</t>
-  </si>
-  <si>
-    <t>0.0011,0.9857,0.0036,0.0238</t>
-  </si>
-  <si>
-    <t>0.0408,0.8874,0.0555,0.0648</t>
-  </si>
-  <si>
-    <t>0.0018,0.8954,0.9296,0.0009</t>
-  </si>
-  <si>
-    <t>0.1186,0.9165,0.0171,0.0005</t>
-  </si>
-  <si>
-    <t>0.5731,0.4485,0.0300,0.0005</t>
-  </si>
-  <si>
-    <t>0.5712,0.5538,0.0154,0.0007</t>
-  </si>
-  <si>
-    <t>0.9930,0.0055,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9906,0.0018,0.0001,0.0018</t>
-  </si>
-  <si>
-    <t>0.9888,0.0018,0.0009,0.0030</t>
-  </si>
-  <si>
-    <t>0.9888,0.0057,0.0006,0.0010</t>
-  </si>
-  <si>
-    <t>0.9942,0.0010,0.0001,0.0014</t>
-  </si>
-  <si>
-    <t>0.9838,0.0062,0.0093,0.0011</t>
-  </si>
-  <si>
-    <t>0.9929,0.0009,0.0001,0.0020</t>
-  </si>
-  <si>
-    <t>0.9930,0.0018,0.0006,0.0010</t>
-  </si>
-  <si>
-    <t>0.0055,0.6703,0.8987,0.0008</t>
-  </si>
-  <si>
-    <t>0.0032,0.9232,0.5161,0.0013</t>
-  </si>
-  <si>
-    <t>0.0068,0.3009,0.9352,0.0022</t>
-  </si>
-  <si>
-    <t>0.0493,0.1202,0.8548,0.0090</t>
-  </si>
-  <si>
-    <t>0.8545,0.0645,0.0452,0.0264</t>
-  </si>
-  <si>
-    <t>0.3105,0.1214,0.5824,0.0183</t>
-  </si>
-  <si>
-    <t>0.6458,0.0042,0.5751,0.0093</t>
-  </si>
-  <si>
-    <t>0.6701,0.0782,0.3237,0.0300</t>
-  </si>
-  <si>
-    <t>0.1956,0.0276,0.0032,0.8774</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0116,0.0087,0.0033,0.9929</t>
-  </si>
-  <si>
-    <t>0.0232,0.0024,0.0014,0.9915</t>
-  </si>
-  <si>
-    <t>0.0050,0.7904,0.8663,0.0009</t>
-  </si>
-  <si>
-    <t>0.9812,0.0080,0.0005,0.0026</t>
-  </si>
-  <si>
-    <t>0.2608,0.7768,0.0034,0.0081</t>
-  </si>
-  <si>
-    <t>0.9577,0.0185,0.0008,0.0069</t>
-  </si>
-  <si>
-    <t>0.8537,0.1814,0.0189,0.0021</t>
-  </si>
-  <si>
-    <t>0.9781,0.0025,0.0006,0.0091</t>
-  </si>
-  <si>
-    <t>0.6727,0.0308,0.0191,0.3486</t>
-  </si>
-  <si>
-    <t>0.9539,0.0118,0.0099,0.0118</t>
-  </si>
-  <si>
-    <t>0.0018,0.6225,0.9313,0.0035</t>
-  </si>
-  <si>
-    <t>0.7073,0.0004,0.0194,0.2261</t>
-  </si>
-  <si>
-    <t>0.9437,0.0042,0.0069,0.0354</t>
-  </si>
-  <si>
-    <t>0.0761,0.9274,0.0061,0.0016</t>
-  </si>
-  <si>
-    <t>0.4116,0.6074,0.0148,0.0296</t>
-  </si>
-  <si>
-    <t>0.8982,0.0836,0.0423,0.0014</t>
-  </si>
-  <si>
-    <t>0.5355,0.4316,0.0352,0.0294</t>
-  </si>
-  <si>
-    <t>0.8990,0.0824,0.0054,0.0056</t>
-  </si>
-  <si>
-    <t>0.8219,0.1332,0.0517,0.0128</t>
-  </si>
-  <si>
-    <t>0.9905,0.0009,0.0001,0.0039</t>
-  </si>
-  <si>
-    <t>0.9857,0.0065,0.0012,0.0012</t>
-  </si>
-  <si>
-    <t>0.9829,0.0051,0.0030,0.0027</t>
-  </si>
-  <si>
-    <t>0.9924,0.0012,0.0008,0.0018</t>
-  </si>
-  <si>
-    <t>0.9686,0.0085,0.0022,0.0068</t>
-  </si>
-  <si>
-    <t>0.9904,0.0024,0.0002,0.0015</t>
-  </si>
-  <si>
-    <t>0.9924,0.0017,0.0003,0.0016</t>
-  </si>
-  <si>
-    <t>0.9866,0.0061,0.0005,0.0014</t>
-  </si>
-  <si>
-    <t>0.1917,0.8460,0.0070,0.0037</t>
-  </si>
-  <si>
-    <t>0.5764,0.5230,0.0180,0.0028</t>
-  </si>
-  <si>
-    <t>0.5413,0.5564,0.0168,0.0017</t>
-  </si>
-  <si>
-    <t>0.6529,0.1907,0.2328,0.0067</t>
-  </si>
-  <si>
-    <t>0.9860,0.0119,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9668,0.0223,0.0037,0.0020</t>
-  </si>
-  <si>
-    <t>0.9545,0.0339,0.0070,0.0032</t>
-  </si>
-  <si>
-    <t>0.9058,0.1184,0.0028,0.0022</t>
-  </si>
-  <si>
-    <t>0.0011,0.0659,0.9950,0.0002</t>
-  </si>
-  <si>
-    <t>0.9466,0.0408,0.0065,0.0034</t>
-  </si>
-  <si>
-    <t>0.0021,0.0071,0.9952,0.0003</t>
-  </si>
-  <si>
-    <t>0.0207,0.2605,0.8834,0.0068</t>
-  </si>
-  <si>
-    <t>0.0239,0.0187,0.9637,0.0022</t>
-  </si>
-  <si>
-    <t>0.0022,0.1174,0.9149,0.0175</t>
-  </si>
-  <si>
-    <t>0.0281,0.0256,0.9610,0.0031</t>
-  </si>
-  <si>
-    <t>0.0058,0.0045,0.9932,0.0003</t>
-  </si>
-  <si>
-    <t>0.0093,0.0160,0.9850,0.0020</t>
-  </si>
-  <si>
-    <t>0.1088,0.0180,0.9191,0.0057</t>
-  </si>
-  <si>
-    <t>0.0280,0.0292,0.9529,0.0018</t>
-  </si>
-  <si>
-    <t>0.3538,0.0698,0.6547,0.0206</t>
-  </si>
-  <si>
-    <t>0.7782,0.0845,0.1713,0.0099</t>
-  </si>
-  <si>
-    <t>0.0668,0.6778,0.3864,0.0049</t>
-  </si>
-  <si>
-    <t>0.3791,0.5571,0.1390,0.0741</t>
-  </si>
-  <si>
-    <t>0.6615,0.0726,0.3206,0.0349</t>
-  </si>
-  <si>
-    <t>0.1197,0.0455,0.8323,0.0050</t>
-  </si>
-  <si>
-    <t>0.7620,0.3403,0.0094,0.0028</t>
-  </si>
-  <si>
-    <t>0.9168,0.1200,0.0063,0.0006</t>
-  </si>
-  <si>
-    <t>0.9388,0.0616,0.0181,0.0023</t>
-  </si>
-  <si>
-    <t>0.9924,0.0071,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9017,0.1716,0.0031,0.0006</t>
-  </si>
-  <si>
-    <t>0.4820,0.4260,0.1583,0.0389</t>
-  </si>
-  <si>
-    <t>0.7914,0.0186,0.2406,0.0175</t>
-  </si>
-  <si>
-    <t>0.8773,0.0187,0.0303,0.0556</t>
-  </si>
-  <si>
-    <t>0.5015,0.0149,0.6633,0.0099</t>
-  </si>
-  <si>
-    <t>0.7607,0.0164,0.2338,0.0309</t>
-  </si>
-  <si>
-    <t>0.0012,0.0070,0.9797,0.0581</t>
-  </si>
-  <si>
-    <t>0.0877,0.0428,0.8893,0.0070</t>
-  </si>
-  <si>
-    <t>0.0210,0.2175,0.8438,0.0476</t>
-  </si>
-  <si>
-    <t>0.0360,0.1344,0.9181,0.0070</t>
-  </si>
-  <si>
-    <t>0.0042,0.4585,0.8697,0.0002</t>
-  </si>
-  <si>
-    <t>0.9951,0.0025,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9930,0.0046,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9888,0.0014,0.0006,0.0040</t>
-  </si>
-  <si>
-    <t>0.9669,0.0309,0.0022,0.0013</t>
-  </si>
-  <si>
-    <t>0.9909,0.0081,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9950,0.0011,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9847,0.0074,0.0002,0.0012</t>
-  </si>
-  <si>
-    <t>0.9915,0.0060,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.1064,0.0178,0.9319,0.0062</t>
-  </si>
-  <si>
-    <t>0.1146,0.3089,0.6479,0.0157</t>
-  </si>
-  <si>
-    <t>0.7335,0.0767,0.1836,0.0635</t>
-  </si>
-  <si>
-    <t>0.0109,0.0214,0.9836,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.0148,0.9948,0.0026</t>
-  </si>
-  <si>
-    <t>0.0111,0.0809,0.9565,0.0009</t>
-  </si>
-  <si>
-    <t>0.0009,0.0010,0.9961,0.0031</t>
-  </si>
-  <si>
-    <t>0.0556,0.0754,0.8557,0.0063</t>
-  </si>
-  <si>
-    <t>0.0013,0.0086,0.9913,0.0027</t>
-  </si>
-  <si>
-    <t>0.0212,0.0977,0.9246,0.0020</t>
-  </si>
-  <si>
-    <t>0.2180,0.1158,0.7187,0.0174</t>
-  </si>
-  <si>
-    <t>0.7825,0.0233,0.1925,0.0255</t>
-  </si>
-  <si>
-    <t>0.7570,0.0121,0.3133,0.0182</t>
-  </si>
-  <si>
-    <t>0.8334,0.0244,0.1555,0.0193</t>
-  </si>
-  <si>
-    <t>0.9893,0.0062,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9937,0.0043,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9988,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9847,0.0100,0.0032,0.0009</t>
-  </si>
-  <si>
-    <t>0.9952,0.0037,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9945,0.0036,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9947,0.0024,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9956,0.0029,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0448,0.1062,0.8983,0.0046</t>
-  </si>
-  <si>
-    <t>0.0017,0.1240,0.9837,0.0004</t>
-  </si>
-  <si>
-    <t>0.0057,0.0541,0.9686,0.0007</t>
-  </si>
-  <si>
-    <t>0.1161,0.1984,0.7345,0.0349</t>
-  </si>
-  <si>
-    <t>0.0057,0.0026,0.9880,0.0035</t>
-  </si>
-  <si>
-    <t>0.1696,0.1372,0.7237,0.0600</t>
-  </si>
-  <si>
-    <t>0.1076,0.0088,0.9301,0.0025</t>
-  </si>
-  <si>
-    <t>0.0126,0.0240,0.9583,0.0192</t>
-  </si>
-  <si>
-    <t>0.7120,0.0044,0.0286,0.2554</t>
-  </si>
-  <si>
-    <t>0.0224,0.0031,0.0038,0.9878</t>
-  </si>
-  <si>
-    <t>0.0603,0.0061,0.0027,0.9784</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.0030,0.9979</t>
-  </si>
-  <si>
-    <t>0.0065,0.0021,0.0037,0.9937</t>
-  </si>
-  <si>
-    <t>0.6406,0.0529,0.1041,0.2373</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,1,1</t>
+  </si>
+  <si>
+    <t>0.9168,0.0192,0.0195,0.0219</t>
+  </si>
+  <si>
+    <t>0.0083,0.0018,0.0032,0.9949</t>
+  </si>
+  <si>
+    <t>0.7421,0.0694,0.0048,0.1029</t>
+  </si>
+  <si>
+    <t>0.0559,0.0038,0.0045,0.9775</t>
+  </si>
+  <si>
+    <t>0.9978,0.0009,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0007,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9898,0.0066,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.9944,0.0035,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9966,0.0031,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9955,0.0036,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0005,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.8231,0.0211,0.1643,0.0223</t>
+  </si>
+  <si>
+    <t>0.0856,0.0660,0.8957,0.0114</t>
+  </si>
+  <si>
+    <t>0.0790,0.0763,0.8288,0.0005</t>
+  </si>
+  <si>
+    <t>0.1046,0.0595,0.8161,0.0079</t>
+  </si>
+  <si>
+    <t>0.6004,0.0196,0.5079,0.0230</t>
+  </si>
+  <si>
+    <t>0.0404,0.9497,0.0058,0.0036</t>
+  </si>
+  <si>
+    <t>0.1522,0.8882,0.0069,0.0008</t>
+  </si>
+  <si>
+    <t>0.4354,0.6412,0.0093,0.0083</t>
+  </si>
+  <si>
+    <t>0.1810,0.8901,0.0025,0.0006</t>
+  </si>
+  <si>
+    <t>0.0097,0.9848,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.8004,0.0100,0.1594,0.0496</t>
+  </si>
+  <si>
+    <t>0.5414,0.0453,0.3094,0.1335</t>
+  </si>
+  <si>
+    <t>0.0740,0.0056,0.9263,0.0182</t>
+  </si>
+  <si>
+    <t>0.2220,0.0082,0.8848,0.0020</t>
+  </si>
+  <si>
+    <t>0.0777,0.0167,0.9255,0.0022</t>
+  </si>
+  <si>
+    <t>0.0203,0.0053,0.9668,0.0202</t>
+  </si>
+  <si>
+    <t>0.0045,0.0012,0.9871,0.0153</t>
+  </si>
+  <si>
+    <t>0.1791,0.8607,0.0055,0.0038</t>
+  </si>
+  <si>
+    <t>0.4914,0.2735,0.3010,0.0135</t>
+  </si>
+  <si>
+    <t>0.0031,0.0056,0.9897,0.0048</t>
+  </si>
+  <si>
+    <t>0.0432,0.7327,0.4272,0.0007</t>
+  </si>
+  <si>
+    <t>0.8590,0.1181,0.0240,0.0082</t>
+  </si>
+  <si>
+    <t>0.8545,0.0956,0.0550,0.0086</t>
+  </si>
+  <si>
+    <t>0.3726,0.7572,0.0041,0.0014</t>
+  </si>
+  <si>
+    <t>0.0212,0.9471,0.0550,0.0093</t>
+  </si>
+  <si>
+    <t>0.0050,0.5210,0.6924,0.0231</t>
+  </si>
+  <si>
+    <t>0.0047,0.0347,0.9152,0.1323</t>
+  </si>
+  <si>
+    <t>0.0415,0.1537,0.8867,0.0038</t>
+  </si>
+  <si>
+    <t>0.0145,0.0219,0.9514,0.0176</t>
+  </si>
+  <si>
+    <t>0.0367,0.2864,0.8184,0.0060</t>
+  </si>
+  <si>
+    <t>0.0219,0.8125,0.4375,0.0019</t>
+  </si>
+  <si>
+    <t>0.0118,0.0298,0.9753,0.0048</t>
+  </si>
+  <si>
+    <t>0.0979,0.4002,0.0265,0.8315</t>
+  </si>
+  <si>
+    <t>0.0029,0.9833,0.0039,0.0111</t>
+  </si>
+  <si>
+    <t>0.0063,0.9652,0.0521,0.0058</t>
+  </si>
+  <si>
+    <t>0.0009,0.9839,0.0022,0.0378</t>
+  </si>
+  <si>
+    <t>0.0033,0.0688,0.9767,0.0078</t>
+  </si>
+  <si>
+    <t>0.0012,0.0678,0.9954,0.0001</t>
+  </si>
+  <si>
+    <t>0.2271,0.0159,0.8288,0.0083</t>
+  </si>
+  <si>
+    <t>0.0552,0.0019,0.9745,0.0021</t>
+  </si>
+  <si>
+    <t>0.0007,0.0034,0.9956,0.0013</t>
+  </si>
+  <si>
+    <t>0.0075,0.0130,0.9848,0.0009</t>
+  </si>
+  <si>
+    <t>0.8328,0.2234,0.0118,0.0021</t>
+  </si>
+  <si>
+    <t>0.9427,0.0314,0.0268,0.0027</t>
+  </si>
+  <si>
+    <t>0.9861,0.0066,0.0021,0.0012</t>
+  </si>
+  <si>
+    <t>0.0012,0.0123,0.9910,0.0139</t>
+  </si>
+  <si>
+    <t>0.9919,0.0023,0.0011,0.0010</t>
+  </si>
+  <si>
+    <t>0.9922,0.0070,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9539,0.0669,0.0031,0.0014</t>
+  </si>
+  <si>
+    <t>0.0003,0.3960,0.9951,0.0001</t>
+  </si>
+  <si>
+    <t>0.0038,0.1240,0.9876,0.0006</t>
+  </si>
+  <si>
+    <t>0.0064,0.1656,0.9210,0.0276</t>
+  </si>
+  <si>
+    <t>0.0004,0.8834,0.9677,0.0001</t>
+  </si>
+  <si>
+    <t>0.0106,0.0322,0.9843,0.0012</t>
+  </si>
+  <si>
+    <t>0.1946,0.8252,0.0468,0.0032</t>
+  </si>
+  <si>
+    <t>0.0870,0.9177,0.0154,0.0017</t>
+  </si>
+  <si>
+    <t>0.8504,0.0493,0.1130,0.0076</t>
+  </si>
+  <si>
+    <t>0.9161,0.0529,0.0403,0.0032</t>
+  </si>
+  <si>
+    <t>0.0024,0.0383,0.9911,0.0013</t>
+  </si>
+  <si>
+    <t>0.0017,0.8261,0.8934,0.0004</t>
+  </si>
+  <si>
+    <t>0.0020,0.8442,0.8906,0.0005</t>
+  </si>
+  <si>
+    <t>0.0011,0.9684,0.5797,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.9287,0.9313,0.0003</t>
+  </si>
+  <si>
+    <t>0.0654,0.0016,0.0038,0.9757</t>
+  </si>
+  <si>
+    <t>0.0009,0.0073,0.0010,0.9989</t>
+  </si>
+  <si>
+    <t>0.0273,0.0013,0.0008,0.9914</t>
+  </si>
+  <si>
+    <t>0.0272,0.0009,0.0082,0.9829</t>
+  </si>
+  <si>
+    <t>0.0684,0.0015,0.0287,0.9359</t>
+  </si>
+  <si>
+    <t>0.0146,0.0041,0.0042,0.9893</t>
+  </si>
+  <si>
+    <t>0.0032,0.9205,0.7138,0.0006</t>
+  </si>
+  <si>
+    <t>0.0012,0.9102,0.8579,0.0001</t>
+  </si>
+  <si>
+    <t>0.0121,0.7316,0.7282,0.0045</t>
+  </si>
+  <si>
+    <t>0.0077,0.8009,0.7548,0.0037</t>
+  </si>
+  <si>
+    <t>0.0006,0.8731,0.9067,0.0001</t>
+  </si>
+  <si>
+    <t>0.0057,0.8471,0.6990,0.0012</t>
+  </si>
+  <si>
+    <t>0.9961,0.0010,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9846,0.0127,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.9829,0.0191,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9943,0.0032,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9914,0.0047,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9957,0.0030,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9907,0.0033,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9905,0.0021,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.9946,0.0015,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9976,0.0009,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9976,0.0007,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9960,0.0006,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9946,0.0019,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9969,0.0012,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0041,0.0122,0.9880,0.0045</t>
+  </si>
+  <si>
+    <t>0.1530,0.2078,0.6328,0.0131</t>
+  </si>
+  <si>
+    <t>0.8979,0.0032,0.0050,0.0699</t>
+  </si>
+  <si>
+    <t>0.0925,0.0344,0.7946,0.1687</t>
+  </si>
+  <si>
+    <t>0.0595,0.9358,0.0030,0.0012</t>
+  </si>
+  <si>
+    <t>0.0745,0.9249,0.0041,0.0021</t>
+  </si>
+  <si>
+    <t>0.0808,0.9082,0.0032,0.0033</t>
+  </si>
+  <si>
+    <t>0.2470,0.8051,0.0029,0.0030</t>
+  </si>
+  <si>
+    <t>0.2720,0.8050,0.0051,0.0034</t>
+  </si>
+  <si>
+    <t>0.0304,0.9629,0.0049,0.0004</t>
+  </si>
+  <si>
+    <t>0.4240,0.6955,0.0024,0.0019</t>
+  </si>
+  <si>
+    <t>0.4607,0.2667,0.3582,0.0786</t>
+  </si>
+  <si>
+    <t>0.2776,0.0307,0.7879,0.0062</t>
+  </si>
+  <si>
+    <t>0.3284,0.5000,0.1592,0.0124</t>
+  </si>
+  <si>
+    <t>0.7557,0.0930,0.1928,0.0155</t>
+  </si>
+  <si>
+    <t>0.6199,0.1156,0.2645,0.1448</t>
+  </si>
+  <si>
+    <t>0.0340,0.9473,0.0434,0.0037</t>
+  </si>
+  <si>
+    <t>0.0036,0.9688,0.0028,0.0763</t>
+  </si>
+  <si>
+    <t>0.0616,0.8932,0.0180,0.0317</t>
+  </si>
+  <si>
+    <t>0.0011,0.8387,0.9626,0.0005</t>
+  </si>
+  <si>
+    <t>0.1207,0.9088,0.0181,0.0009</t>
+  </si>
+  <si>
+    <t>0.5193,0.6112,0.0111,0.0011</t>
+  </si>
+  <si>
+    <t>0.6296,0.4411,0.0220,0.0012</t>
+  </si>
+  <si>
+    <t>0.9898,0.0094,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9845,0.0035,0.0002,0.0032</t>
+  </si>
+  <si>
+    <t>0.9853,0.0012,0.0004,0.0085</t>
+  </si>
+  <si>
+    <t>0.9850,0.0039,0.0011,0.0025</t>
+  </si>
+  <si>
+    <t>0.9804,0.0089,0.0050,0.0029</t>
+  </si>
+  <si>
+    <t>0.9543,0.0199,0.0278,0.0021</t>
+  </si>
+  <si>
+    <t>0.9933,0.0008,0.0004,0.0018</t>
+  </si>
+  <si>
+    <t>0.9583,0.0638,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.0049,0.6425,0.8993,0.0004</t>
+  </si>
+  <si>
+    <t>0.0024,0.9482,0.3404,0.0002</t>
+  </si>
+  <si>
+    <t>0.0085,0.0461,0.9825,0.0009</t>
+  </si>
+  <si>
+    <t>0.0609,0.4090,0.5128,0.0047</t>
+  </si>
+  <si>
+    <t>0.8669,0.0147,0.0464,0.0561</t>
+  </si>
+  <si>
+    <t>0.6031,0.1566,0.3700,0.0481</t>
+  </si>
+  <si>
+    <t>0.5428,0.0210,0.6159,0.0059</t>
+  </si>
+  <si>
+    <t>0.7297,0.1469,0.0840,0.0239</t>
+  </si>
+  <si>
+    <t>0.1195,0.0084,0.0050,0.9463</t>
+  </si>
+  <si>
+    <t>0.0025,0.0001,0.0010,0.9981</t>
+  </si>
+  <si>
+    <t>0.0087,0.0152,0.0016,0.9943</t>
+  </si>
+  <si>
+    <t>0.0153,0.0013,0.0017,0.9932</t>
+  </si>
+  <si>
+    <t>0.0123,0.6437,0.6873,0.0116</t>
+  </si>
+  <si>
+    <t>0.9682,0.0155,0.0022,0.0044</t>
+  </si>
+  <si>
+    <t>0.8354,0.1728,0.0238,0.0071</t>
+  </si>
+  <si>
+    <t>0.9809,0.0089,0.0044,0.0014</t>
+  </si>
+  <si>
+    <t>0.9432,0.0595,0.0068,0.0025</t>
+  </si>
+  <si>
+    <t>0.9768,0.0080,0.0014,0.0036</t>
+  </si>
+  <si>
+    <t>0.2779,0.0062,0.0809,0.6989</t>
+  </si>
+  <si>
+    <t>0.9570,0.0153,0.0041,0.0088</t>
+  </si>
+  <si>
+    <t>0.0026,0.1915,0.9608,0.0061</t>
+  </si>
+  <si>
+    <t>0.9164,0.0015,0.0281,0.0261</t>
+  </si>
+  <si>
+    <t>0.9897,0.0004,0.0005,0.0074</t>
+  </si>
+  <si>
+    <t>0.3599,0.6642,0.0390,0.0220</t>
+  </si>
+  <si>
+    <t>0.8572,0.1637,0.0033,0.0050</t>
+  </si>
+  <si>
+    <t>0.7985,0.1490,0.0659,0.0185</t>
+  </si>
+  <si>
+    <t>0.6047,0.4328,0.0159,0.0098</t>
+  </si>
+  <si>
+    <t>0.7442,0.1042,0.2401,0.0164</t>
+  </si>
+  <si>
+    <t>0.8631,0.1016,0.0482,0.0097</t>
+  </si>
+  <si>
+    <t>0.9745,0.0033,0.0003,0.0097</t>
+  </si>
+  <si>
+    <t>0.9854,0.0043,0.0004,0.0024</t>
+  </si>
+  <si>
+    <t>0.9957,0.0019,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9942,0.0005,0.0002,0.0022</t>
+  </si>
+  <si>
+    <t>0.9815,0.0075,0.0021,0.0023</t>
+  </si>
+  <si>
+    <t>0.9910,0.0009,0.0001,0.0028</t>
+  </si>
+  <si>
+    <t>0.9954,0.0004,0.0001,0.0016</t>
+  </si>
+  <si>
+    <t>0.9927,0.0006,0.0002,0.0036</t>
+  </si>
+  <si>
+    <t>0.1331,0.8602,0.0032,0.0063</t>
+  </si>
+  <si>
+    <t>0.7104,0.3701,0.0177,0.0014</t>
+  </si>
+  <si>
+    <t>0.4695,0.6485,0.0093,0.0016</t>
+  </si>
+  <si>
+    <t>0.1578,0.2505,0.7325,0.0037</t>
+  </si>
+  <si>
+    <t>0.9740,0.0227,0.0009,0.0015</t>
+  </si>
+  <si>
+    <t>0.9722,0.0167,0.0062,0.0023</t>
+  </si>
+  <si>
+    <t>0.9542,0.0371,0.0004,0.0022</t>
+  </si>
+  <si>
+    <t>0.6397,0.4381,0.0084,0.0047</t>
+  </si>
+  <si>
+    <t>0.0064,0.0371,0.9885,0.0011</t>
+  </si>
+  <si>
+    <t>0.9556,0.0407,0.0053,0.0030</t>
+  </si>
+  <si>
+    <t>0.0008,0.0074,0.9963,0.0003</t>
+  </si>
+  <si>
+    <t>0.0137,0.5154,0.9120,0.0070</t>
+  </si>
+  <si>
+    <t>0.0039,0.0027,0.9930,0.0010</t>
+  </si>
+  <si>
+    <t>0.0088,0.0153,0.9814,0.0038</t>
+  </si>
+  <si>
+    <t>0.0173,0.0094,0.9780,0.0059</t>
+  </si>
+  <si>
+    <t>0.0028,0.0007,0.9965,0.0008</t>
+  </si>
+  <si>
+    <t>0.0367,0.0112,0.9566,0.0045</t>
+  </si>
+  <si>
+    <t>0.2036,0.1979,0.6567,0.0427</t>
+  </si>
+  <si>
+    <t>0.0568,0.0207,0.9430,0.0032</t>
+  </si>
+  <si>
+    <t>0.6067,0.0694,0.4225,0.0197</t>
+  </si>
+  <si>
+    <t>0.2581,0.0607,0.7204,0.0035</t>
+  </si>
+  <si>
+    <t>0.0379,0.3922,0.7583,0.0034</t>
+  </si>
+  <si>
+    <t>0.5700,0.1675,0.2856,0.0659</t>
+  </si>
+  <si>
+    <t>0.4586,0.4209,0.1998,0.0121</t>
+  </si>
+  <si>
+    <t>0.3190,0.0367,0.7162,0.0523</t>
+  </si>
+  <si>
+    <t>0.8702,0.2077,0.0061,0.0005</t>
+  </si>
+  <si>
+    <t>0.9446,0.0723,0.0110,0.0004</t>
+  </si>
+  <si>
+    <t>0.9731,0.0190,0.0073,0.0015</t>
+  </si>
+  <si>
+    <t>0.9938,0.0022,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9682,0.0363,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.8592,0.0202,0.1440,0.0087</t>
+  </si>
+  <si>
+    <t>0.7773,0.0066,0.3104,0.0091</t>
+  </si>
+  <si>
+    <t>0.1365,0.5453,0.0138,0.4648</t>
+  </si>
+  <si>
+    <t>0.5744,0.0387,0.4186,0.0479</t>
+  </si>
+  <si>
+    <t>0.4588,0.0043,0.4699,0.0781</t>
+  </si>
+  <si>
+    <t>0.0043,0.0035,0.9888,0.0118</t>
+  </si>
+  <si>
+    <t>0.0199,0.4056,0.8284,0.0033</t>
+  </si>
+  <si>
+    <t>0.0204,0.4665,0.8622,0.0086</t>
+  </si>
+  <si>
+    <t>0.2445,0.0935,0.6929,0.0139</t>
+  </si>
+  <si>
+    <t>0.0216,0.8244,0.2906,0.0074</t>
+  </si>
+  <si>
+    <t>0.9935,0.0009,0.0001,0.0018</t>
+  </si>
+  <si>
+    <t>0.9905,0.0062,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9917,0.0046,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9952,0.0020,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9829,0.0143,0.0012,0.0012</t>
+  </si>
+  <si>
+    <t>0.9768,0.0175,0.0018,0.0013</t>
+  </si>
+  <si>
+    <t>0.9832,0.0069,0.0003,0.0017</t>
+  </si>
+  <si>
+    <t>0.9893,0.0031,0.0013,0.0015</t>
+  </si>
+  <si>
+    <t>0.0659,0.0123,0.9578,0.0028</t>
+  </si>
+  <si>
+    <t>0.1866,0.1774,0.6803,0.0069</t>
+  </si>
+  <si>
+    <t>0.8528,0.0314,0.1238,0.0163</t>
+  </si>
+  <si>
+    <t>0.0407,0.0142,0.9501,0.0037</t>
+  </si>
+  <si>
+    <t>0.0001,0.0029,0.9989,0.0006</t>
+  </si>
+  <si>
+    <t>0.0152,0.0475,0.9511,0.0033</t>
+  </si>
+  <si>
+    <t>0.0002,0.0035,0.9985,0.0005</t>
+  </si>
+  <si>
+    <t>0.0364,0.0089,0.9550,0.0079</t>
+  </si>
+  <si>
+    <t>0.0005,0.0008,0.9926,0.0152</t>
+  </si>
+  <si>
+    <t>0.0480,0.0355,0.9105,0.0027</t>
+  </si>
+  <si>
+    <t>0.0412,0.0272,0.9339,0.0018</t>
+  </si>
+  <si>
+    <t>0.8878,0.0024,0.0428,0.0494</t>
+  </si>
+  <si>
+    <t>0.5041,0.0051,0.7158,0.0047</t>
+  </si>
+  <si>
+    <t>0.9102,0.0087,0.0562,0.0139</t>
+  </si>
+  <si>
+    <t>0.9929,0.0024,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9884,0.0053,0.0009,0.0013</t>
+  </si>
+  <si>
+    <t>0.9970,0.0014,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9930,0.0041,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9941,0.0005,0.0001,0.0021</t>
+  </si>
+  <si>
+    <t>0.9958,0.0029,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9958,0.0014,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9929,0.0032,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.0218,0.3663,0.8031,0.0018</t>
+  </si>
+  <si>
+    <t>0.0032,0.0468,0.9840,0.0007</t>
+  </si>
+  <si>
+    <t>0.0035,0.0085,0.9799,0.0225</t>
+  </si>
+  <si>
+    <t>0.1470,0.0192,0.8357,0.0028</t>
+  </si>
+  <si>
+    <t>0.1445,0.0132,0.8963,0.0072</t>
+  </si>
+  <si>
+    <t>0.0240,0.0363,0.6914,0.5460</t>
+  </si>
+  <si>
+    <t>0.0833,0.0190,0.9100,0.0024</t>
+  </si>
+  <si>
+    <t>0.0941,0.0259,0.7009,0.1666</t>
+  </si>
+  <si>
+    <t>0.4743,0.0007,0.0116,0.6189</t>
+  </si>
+  <si>
+    <t>0.0098,0.0081,0.0009,0.9953</t>
+  </si>
+  <si>
+    <t>0.0273,0.0299,0.0012,0.9837</t>
+  </si>
+  <si>
+    <t>0.0207,0.0005,0.0010,0.9921</t>
+  </si>
+  <si>
+    <t>0.0079,0.0003,0.0023,0.9951</t>
+  </si>
+  <si>
+    <t>0.7642,0.0890,0.0146,0.0936</t>
   </si>
 </sst>
 </file>
@@ -1953,10 +1965,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2189,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2819,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,10 +2847,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2917,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2990,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3561,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3620,7 @@
         <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3701,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3925,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,10 +4121,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4165,10 +4177,10 @@
         <v>259</v>
       </c>
       <c r="C160" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4208,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4362,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4390,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4513,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4807,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4905,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
